--- a/wiki/reports/daily/2026-09-16_일일보고.xlsx
+++ b/wiki/reports/daily/2026-09-16_일일보고.xlsx
@@ -76,7 +76,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -91,6 +91,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D6E4F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F5E3"/>
       </patternFill>
     </fill>
     <fill>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -179,25 +184,31 @@
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -209,19 +220,19 @@
     <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -613,7 +624,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성: 2026-09-16 07:59   |   전일: 9월 15일   |   월평균 기준: 이전 작업일 11일 평균   |   9월 누적 작업일: 12일</t>
+          <t>생성: 2026-09-16 16:00   |   전일: 9월 15일   |   월평균 기준: 이전 작업일 11일 평균   |   9월 누적 작업일: 12일</t>
         </is>
       </c>
     </row>
@@ -675,27 +686,27 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>13</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>-10</v>
+        <v>13</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-0.7692307692307693</v>
+        <v>1</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>30.4</v>
       </c>
-      <c r="G4" s="7" t="n">
-        <v>-27.36363636363636</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>-0.9011976047904192</v>
-      </c>
-      <c r="I4" s="10" t="inlineStr"/>
+      <c r="G4" s="10" t="n">
+        <v>-4.363636363636363</v>
+      </c>
+      <c r="H4" s="11" t="n">
+        <v>-0.1437125748502994</v>
+      </c>
+      <c r="I4" s="12" t="inlineStr"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -704,205 +715,205 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>546</v>
+        <v>9011</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>3386</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>-2840</v>
+        <v>5625</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>-0.8387477849970466</v>
+        <v>1.661252215002953</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>7322.5</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-6776.545454545455</v>
+        <v>1688.454545454545</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>-0.9254357650096837</v>
-      </c>
-      <c r="I5" s="10" t="inlineStr">
-        <is>
-          <t>0:09:06</t>
+        <v>0.230583006406118</v>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>2:30:11</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>GX7  수량 (개)</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>-0.5</v>
+        <v>5.5</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>14.7</v>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>-13.72727272727273</v>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>-0.9320987654320988</v>
-      </c>
-      <c r="I6" s="10" t="inlineStr"/>
+      <c r="G6" s="10" t="n">
+        <v>-1.727272727272727</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>-0.1172839506172839</v>
+      </c>
+      <c r="I6" s="12" t="inlineStr"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>GX7  가공시간 (초)</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>306</v>
+        <v>4433</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>609</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>-303</v>
+        <v>3824</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-0.4975369458128079</v>
+        <v>6.279146141215107</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>5439.5</v>
       </c>
-      <c r="G7" s="7" t="n">
-        <v>-5133.545454545455</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>-0.943745299573828</v>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>0:05:06</t>
+      <c r="G7" s="10" t="n">
+        <v>-1006.545454545455</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>-0.1850421993816329</v>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>1:13:53</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>합계  수량 (개)</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>15</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>-11</v>
+        <v>24</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-0.7333333333333333</v>
+        <v>1.6</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>45.1</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>-41.09090909090909</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>-0.9112903225806451</v>
-      </c>
-      <c r="I8" s="10" t="inlineStr"/>
+      <c r="G8" s="10" t="n">
+        <v>-6.090909090909093</v>
+      </c>
+      <c r="H8" s="11" t="n">
+        <v>-0.1350806451612904</v>
+      </c>
+      <c r="I8" s="12" t="inlineStr"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>합계  가공시간 (초)</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>852</v>
+        <v>13444</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>3995</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>-3143</v>
+        <v>9449</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>-0.7867334167709638</v>
+        <v>2.365206508135169</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>12762.1</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-11910.09090909091</v>
+        <v>681.9090909090901</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>-0.9332397797454107</v>
-      </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>0:14:12</t>
+        <v>0.05343239566044315</v>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>3:44:04</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>합계  금액</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>15</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>-11</v>
+        <v>24</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>-0.7333333333333333</v>
+        <v>1.6</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>43.9</v>
       </c>
-      <c r="G10" s="7" t="n">
-        <v>-39.90909090909091</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>-0.9089026915113871</v>
-      </c>
-      <c r="I10" s="10" t="inlineStr"/>
+      <c r="G10" s="10" t="n">
+        <v>-4.909090909090907</v>
+      </c>
+      <c r="H10" s="11" t="n">
+        <v>-0.1118012422360248</v>
+      </c>
+      <c r="I10" s="12" t="inlineStr"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>9월 누적  (12일 / 16일 중 작업일)</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>141235</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>487</v>
-      </c>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="13" t="n"/>
-      <c r="I11" s="13" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="16" t="n">
+        <v>535</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>153827</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>522</v>
+      </c>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="15" t="n"/>
+      <c r="H11" s="15" t="n"/>
+      <c r="I11" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -920,7 +931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -944,271 +955,845 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>■ FAST GRIND</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>형상</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>날수(F)</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>날경(Ø)</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>상크경(Ø)</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>코팅</t>
         </is>
       </c>
-      <c r="G3" s="16" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>특이사항</t>
         </is>
       </c>
-      <c r="H3" s="16" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I3" s="16" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>수량(개)</t>
         </is>
       </c>
-      <c r="J3" s="16" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>시간합계(초)</t>
         </is>
       </c>
-      <c r="K3" s="16" t="inlineStr">
+      <c r="K3" s="18" t="inlineStr">
         <is>
           <t>시간(H:M:S)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="17" t="n">
+      <c r="A4" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>비</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
+      <c r="G4" s="20" t="inlineStr">
         <is>
           <t>재가공</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr"/>
-      <c r="I4" s="19" t="n">
+      <c r="H4" s="19" t="inlineStr"/>
+      <c r="I4" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="19" t="n">
+      <c r="J4" s="21" t="n">
         <v>546</v>
       </c>
-      <c r="K4" s="17" t="inlineStr">
+      <c r="K4" s="19" t="inlineStr">
         <is>
           <t>0:09:06</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>R0.5</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>재가공</t>
+        </is>
+      </c>
+      <c r="H5" s="19" t="inlineStr"/>
+      <c r="I5" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" s="21" t="n">
+        <v>768</v>
+      </c>
+      <c r="K5" s="19" t="inlineStr">
+        <is>
+          <t>0:12:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>R0.5</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="H6" s="19" t="inlineStr"/>
+      <c r="I6" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="21" t="n">
+        <v>498</v>
+      </c>
+      <c r="K6" s="19" t="inlineStr">
+        <is>
+          <t>0:08:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>0301</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="inlineStr"/>
+      <c r="I7" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" s="21" t="n">
+        <v>480</v>
+      </c>
+      <c r="K7" s="19" t="inlineStr">
+        <is>
+          <t>0:08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>0301</t>
+        </is>
+      </c>
+      <c r="H8" s="19" t="inlineStr"/>
+      <c r="I8" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="21" t="n">
+        <v>310</v>
+      </c>
+      <c r="K8" s="19" t="inlineStr">
+        <is>
+          <t>0:05:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>R0.5</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="H9" s="19" t="inlineStr"/>
+      <c r="I9" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="J9" s="21" t="n">
+        <v>6409</v>
+      </c>
+      <c r="K9" s="19" t="inlineStr">
+        <is>
+          <t>1:46:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>FAST GRIND 소계</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="14" t="n">
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="15" t="n"/>
+      <c r="I10" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="J10" s="16" t="n">
+        <v>9011</v>
+      </c>
+      <c r="K10" s="15" t="inlineStr">
+        <is>
+          <t>2:30:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>■ GX7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>순서</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>형상</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>날수(F)</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>날경(Ø)</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>상크경(Ø)</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>코팅</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>특이사항</t>
+        </is>
+      </c>
+      <c r="H13" s="23" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I13" s="23" t="inlineStr">
+        <is>
+          <t>수량(개)</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="inlineStr">
+        <is>
+          <t>시간합계(초)</t>
+        </is>
+      </c>
+      <c r="K13" s="23" t="inlineStr">
+        <is>
+          <t>시간(H:M:S)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E14" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="F14" s="25" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G14" s="25" t="inlineStr">
+        <is>
+          <t>0189</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr"/>
+      <c r="I14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="26" t="n">
+        <v>306</v>
+      </c>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>0:05:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="24" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="E15" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="F15" s="25" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G15" s="25" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr"/>
+      <c r="I15" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="26" t="n">
+        <v>306</v>
+      </c>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>0:05:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J5" s="14" t="n">
-        <v>546</v>
-      </c>
-      <c r="K5" s="13" t="inlineStr">
-        <is>
-          <t>0:09:06</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>■ GX7</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>순서</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>형상</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>날수(F)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>날경(Ø)</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="inlineStr">
-        <is>
-          <t>상크경(Ø)</t>
-        </is>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t>코팅</t>
-        </is>
-      </c>
-      <c r="G8" s="21" t="inlineStr">
-        <is>
-          <t>특이사항</t>
-        </is>
-      </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I8" s="21" t="inlineStr">
-        <is>
-          <t>수량(개)</t>
-        </is>
-      </c>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t>시간합계(초)</t>
-        </is>
-      </c>
-      <c r="K8" s="21" t="inlineStr">
-        <is>
-          <t>시간(H:M:S)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="22" t="n">
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="24" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="E16" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="F16" s="25" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G16" s="25" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr"/>
+      <c r="I16" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="J16" s="26" t="n">
+        <v>314</v>
+      </c>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>0:05:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>드릴</t>
         </is>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C17" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="E9" s="22" t="n">
+      <c r="D17" s="24" t="n">
         <v>11</v>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="E17" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="F17" s="25" t="inlineStr">
         <is>
           <t>뮤</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
-        <is>
-          <t>0189</t>
-        </is>
-      </c>
-      <c r="H9" s="22" t="inlineStr"/>
-      <c r="I9" s="24" t="n">
+      <c r="G17" s="25" t="inlineStr">
+        <is>
+          <t>0300, 0299</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr"/>
+      <c r="I17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" s="26" t="n">
+        <v>948</v>
+      </c>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>0:15:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="24" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="E18" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F18" s="25" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G18" s="25" t="inlineStr">
+        <is>
+          <t>0299</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr"/>
+      <c r="I18" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="24" t="n">
-        <v>306</v>
-      </c>
-      <c r="K9" s="22" t="inlineStr">
-        <is>
-          <t>0:05:06</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="J18" s="26" t="n">
+        <v>326</v>
+      </c>
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>0:05:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="E19" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" s="25" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G19" s="25" t="inlineStr">
+        <is>
+          <t>0300, 0299</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr"/>
+      <c r="I19" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" s="26" t="n">
+        <v>660</v>
+      </c>
+      <c r="K19" s="24" t="inlineStr">
+        <is>
+          <t>0:11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="E20" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F20" s="25" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G20" s="25" t="inlineStr">
+        <is>
+          <t>0299</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr"/>
+      <c r="I20" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="26" t="n">
+        <v>330</v>
+      </c>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>0:05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="24" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="E21" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="F21" s="25" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G21" s="25" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr"/>
+      <c r="I21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="26" t="n">
+        <v>368</v>
+      </c>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>0:06:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="E22" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="F22" s="25" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G22" s="25" t="inlineStr">
+        <is>
+          <t>0299</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr"/>
+      <c r="I22" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="26" t="n">
+        <v>375</v>
+      </c>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>0:06:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E23" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="F23" s="25" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G23" s="25" t="inlineStr">
+        <is>
+          <t>0299</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr"/>
+      <c r="I23" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="26" t="n">
+        <v>500</v>
+      </c>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>0:08:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>GX7 소계</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="13" t="n"/>
-      <c r="I10" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>306</v>
-      </c>
-      <c r="K10" s="13" t="inlineStr">
-        <is>
-          <t>0:05:06</t>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="15" t="n"/>
+      <c r="H24" s="15" t="n"/>
+      <c r="I24" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="J24" s="16" t="n">
+        <v>4433</v>
+      </c>
+      <c r="K24" s="15" t="inlineStr">
+        <is>
+          <t>1:13:53</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A5:H5"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
